--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jackr\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d2a8a3fe962b126f/Desktop/Vokabel App/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74EFB9AC-A90C-4100-BF02-5ACD04C7DC9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{74EFB9AC-A90C-4100-BF02-5ACD04C7DC9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5081CA3C-BDEF-43C1-A987-8475C04EA003}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DFF7D6F0-3BF7-4379-A7F7-CB73CBA2A484}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="182">
   <si>
     <t>la recette</t>
   </si>
@@ -275,6 +275,336 @@
   </si>
   <si>
     <t>l'huile (feminine)</t>
+  </si>
+  <si>
+    <t>beaucoup (de monde)</t>
+  </si>
+  <si>
+    <t>la poire</t>
+  </si>
+  <si>
+    <t>la fleur</t>
+  </si>
+  <si>
+    <t>un ami, une amie</t>
+  </si>
+  <si>
+    <t>rencontrer</t>
+  </si>
+  <si>
+    <t>le garçon (les gars)</t>
+  </si>
+  <si>
+    <t>la banane</t>
+  </si>
+  <si>
+    <t>la fraise</t>
+  </si>
+  <si>
+    <t>la salade</t>
+  </si>
+  <si>
+    <t>le goûter</t>
+  </si>
+  <si>
+    <t>demain</t>
+  </si>
+  <si>
+    <t>la fille</t>
+  </si>
+  <si>
+    <t>la quiche</t>
+  </si>
+  <si>
+    <t>(à) emporter</t>
+  </si>
+  <si>
+    <t>sur place</t>
+  </si>
+  <si>
+    <t>sucré, sucrée</t>
+  </si>
+  <si>
+    <t>le beurre</t>
+  </si>
+  <si>
+    <t>le sucre</t>
+  </si>
+  <si>
+    <t>la glace</t>
+  </si>
+  <si>
+    <t>la chantilly</t>
+  </si>
+  <si>
+    <t>salé, salée</t>
+  </si>
+  <si>
+    <t>le fromage</t>
+  </si>
+  <si>
+    <t>le jambon</t>
+  </si>
+  <si>
+    <t>la boisson</t>
+  </si>
+  <si>
+    <t>une eau minérale</t>
+  </si>
+  <si>
+    <t>la limonade</t>
+  </si>
+  <si>
+    <t>le jus</t>
+  </si>
+  <si>
+    <t>une orange</t>
+  </si>
+  <si>
+    <t>le jus d'orange</t>
+  </si>
+  <si>
+    <t>désirer</t>
+  </si>
+  <si>
+    <t>le parfum</t>
+  </si>
+  <si>
+    <t>(re)venir</t>
+  </si>
+  <si>
+    <t>tout de suite</t>
+  </si>
+  <si>
+    <t>une addition</t>
+  </si>
+  <si>
+    <t>la maison</t>
+  </si>
+  <si>
+    <t>Page 25</t>
+  </si>
+  <si>
+    <t>Page 28</t>
+  </si>
+  <si>
+    <t>viel(e) (viele Leute)</t>
+  </si>
+  <si>
+    <t>die Birne</t>
+  </si>
+  <si>
+    <t>die Blume</t>
+  </si>
+  <si>
+    <t>der Freund, die Freundin</t>
+  </si>
+  <si>
+    <t>treffen, begegnen</t>
+  </si>
+  <si>
+    <t>der Junge (die Jungs)</t>
+  </si>
+  <si>
+    <t>die Banane</t>
+  </si>
+  <si>
+    <t>die Erdbeere</t>
+  </si>
+  <si>
+    <t>der Salat</t>
+  </si>
+  <si>
+    <t>der Nachmittagssnack, die Vesper</t>
+  </si>
+  <si>
+    <t>morgen</t>
+  </si>
+  <si>
+    <t>das Mädchen, die Tochter</t>
+  </si>
+  <si>
+    <t>die Quiche</t>
+  </si>
+  <si>
+    <t>zum Mitnehmen</t>
+  </si>
+  <si>
+    <t>vor Ort / an Platz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">süß </t>
+  </si>
+  <si>
+    <t>die Butter</t>
+  </si>
+  <si>
+    <t>der Zucker</t>
+  </si>
+  <si>
+    <t>das Eis</t>
+  </si>
+  <si>
+    <t>die Schlagsahne</t>
+  </si>
+  <si>
+    <t>herzhaft, salzig</t>
+  </si>
+  <si>
+    <t>der Käse</t>
+  </si>
+  <si>
+    <t>der Schinken</t>
+  </si>
+  <si>
+    <t>mit (z. B. „glace au chocolat" = Eis mit Schokolade)</t>
+  </si>
+  <si>
+    <t>das Getränk</t>
+  </si>
+  <si>
+    <t>das Mineralwasser</t>
+  </si>
+  <si>
+    <t>die Limonade</t>
+  </si>
+  <si>
+    <t>der Saft</t>
+  </si>
+  <si>
+    <t>die Orange</t>
+  </si>
+  <si>
+    <t>der Orangensaft</t>
+  </si>
+  <si>
+    <t>wünschen</t>
+  </si>
+  <si>
+    <t>das Parfüm</t>
+  </si>
+  <si>
+    <t>(zurück)kommen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sofort, gleich </t>
+  </si>
+  <si>
+    <t>die Rechnung</t>
+  </si>
+  <si>
+    <t>das Haus, das Zuhause</t>
+  </si>
+  <si>
+    <t xml:space="preserve">welche/r/s </t>
+  </si>
+  <si>
+    <t>quel, quelle</t>
+  </si>
+  <si>
+    <t>au, à la, aux</t>
+  </si>
+  <si>
+    <t>un paquet</t>
+  </si>
+  <si>
+    <t>un sachet</t>
+  </si>
+  <si>
+    <t>un morceau</t>
+  </si>
+  <si>
+    <t>une bouteille</t>
+  </si>
+  <si>
+    <t>un litre</t>
+  </si>
+  <si>
+    <t>les chips</t>
+  </si>
+  <si>
+    <t>la queue</t>
+  </si>
+  <si>
+    <t>le client, la cliente</t>
+  </si>
+  <si>
+    <t>le caissier, la caissière</t>
+  </si>
+  <si>
+    <t>la caisse</t>
+  </si>
+  <si>
+    <t>le chariot</t>
+  </si>
+  <si>
+    <t>la femme</t>
+  </si>
+  <si>
+    <t>le panier</t>
+  </si>
+  <si>
+    <t>la couverture</t>
+  </si>
+  <si>
+    <t>apporter</t>
+  </si>
+  <si>
+    <t>le sandwich</t>
+  </si>
+  <si>
+    <t>das Paket, die Packung</t>
+  </si>
+  <si>
+    <t>die Tüte, das Päckchen</t>
+  </si>
+  <si>
+    <t>das Stück</t>
+  </si>
+  <si>
+    <t>die Flasche</t>
+  </si>
+  <si>
+    <t>der Liter</t>
+  </si>
+  <si>
+    <t>die Chips</t>
+  </si>
+  <si>
+    <t>die Schlange (Warteschlange)</t>
+  </si>
+  <si>
+    <t>der Kunde, die Kundin</t>
+  </si>
+  <si>
+    <t>der Kassierer, die Kassiererin</t>
+  </si>
+  <si>
+    <t>die Kasse</t>
+  </si>
+  <si>
+    <t>der Einkaufswagen</t>
+  </si>
+  <si>
+    <t>die Frau</t>
+  </si>
+  <si>
+    <t>der Korb</t>
+  </si>
+  <si>
+    <t>die Decke</t>
+  </si>
+  <si>
+    <t>mitbringen, bringen</t>
+  </si>
+  <si>
+    <t>das Sandwich</t>
+  </si>
+  <si>
+    <t>Page 29</t>
+  </si>
+  <si>
+    <t>Page 30</t>
   </si>
 </sst>
 </file>
@@ -349,6 +679,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -668,7 +1002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F1B1B3E-A116-4603-AC6A-0B5745F1B187}">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C89"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.85546875" customWidth="1"/>
@@ -892,7 +1226,7 @@
         <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -903,7 +1237,7 @@
         <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -914,7 +1248,7 @@
         <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -925,7 +1259,7 @@
         <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -936,7 +1270,7 @@
         <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -947,7 +1281,7 @@
         <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -958,7 +1292,7 @@
         <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -969,7 +1303,7 @@
         <v>51</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -980,7 +1314,7 @@
         <v>53</v>
       </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -991,7 +1325,7 @@
         <v>55</v>
       </c>
       <c r="C29" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1002,7 +1336,7 @@
         <v>57</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1013,7 +1347,7 @@
         <v>59</v>
       </c>
       <c r="C31" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1024,7 +1358,7 @@
         <v>61</v>
       </c>
       <c r="C32" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1035,7 +1369,7 @@
         <v>63</v>
       </c>
       <c r="C33" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1046,7 +1380,7 @@
         <v>64</v>
       </c>
       <c r="C34" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1057,7 +1391,590 @@
         <v>66</v>
       </c>
       <c r="C35" t="s">
-        <v>70</v>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C39" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C41" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C42" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C43" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C44" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C45" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C46" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C47" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C48" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C50" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C51" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C52" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C53" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C54" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C55" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C56" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C57" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C58" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C59" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C60" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C61" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C62" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C63" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C64" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C65" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C66" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C67" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C68" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C69" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C70" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C71" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C72" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C73" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C74" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C75" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C76" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C77" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C78" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C79" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C80" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C81" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C82" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C83" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C84" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C85" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C86" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C87" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C88" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C89" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
